--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.22526</v>
+        <v>16.72999</v>
       </c>
       <c r="D2" t="n">
-        <v>16.23515</v>
+        <v>16.40848</v>
       </c>
       <c r="E2" t="n">
-        <v>16.52951</v>
+        <v>16.46842</v>
       </c>
       <c r="F2" t="n">
-        <v>42.63233</v>
+        <v>42.17453</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0503</v>
+        <v>0.05186</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81992</v>
+        <v>1.81043</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.78187</v>
+        <v>16.85658</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69797</v>
+        <v>16.25421</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64776</v>
+        <v>16.54807</v>
       </c>
       <c r="F3" t="n">
-        <v>41.79497</v>
+        <v>41.88001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05009</v>
+        <v>0.05099</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82602</v>
+        <v>1.81391</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.54657</v>
+        <v>17.0217</v>
       </c>
       <c r="D4" t="n">
-        <v>16.19895</v>
+        <v>16.66614</v>
       </c>
       <c r="E4" t="n">
-        <v>16.31886</v>
+        <v>16.68472</v>
       </c>
       <c r="F4" t="n">
-        <v>43.99048</v>
+        <v>42.60188</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05056</v>
+        <v>0.05106</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80029</v>
+        <v>1.79595</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.82419</v>
+        <v>16.79443</v>
       </c>
       <c r="D5" t="n">
-        <v>16.49045</v>
+        <v>16.31655</v>
       </c>
       <c r="E5" t="n">
-        <v>16.45013</v>
+        <v>16.49424</v>
       </c>
       <c r="F5" t="n">
-        <v>42.50471</v>
+        <v>41.27504</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05006</v>
+        <v>0.0496</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79534</v>
+        <v>1.82829</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.76126</v>
+        <v>17.15596</v>
       </c>
       <c r="D6" t="n">
-        <v>16.75434</v>
+        <v>16.58315</v>
       </c>
       <c r="E6" t="n">
-        <v>16.87919</v>
+        <v>16.8466</v>
       </c>
       <c r="F6" t="n">
-        <v>42.62803</v>
+        <v>43.01226</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05046</v>
+        <v>0.05041</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79244</v>
+        <v>1.83764</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.28449</v>
+        <v>16.98594</v>
       </c>
       <c r="D7" t="n">
-        <v>16.35744</v>
+        <v>16.33606</v>
       </c>
       <c r="E7" t="n">
-        <v>16.63945</v>
+        <v>16.56141</v>
       </c>
       <c r="F7" t="n">
-        <v>42.24824</v>
+        <v>42.13385</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05018</v>
+        <v>0.05058</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85108</v>
+        <v>1.82142</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.69321</v>
+        <v>17.06461</v>
       </c>
       <c r="D8" t="n">
-        <v>16.54177</v>
+        <v>16.35549</v>
       </c>
       <c r="E8" t="n">
-        <v>16.87443</v>
+        <v>16.39363</v>
       </c>
       <c r="F8" t="n">
-        <v>41.31173</v>
+        <v>42.86279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05002</v>
+        <v>0.0504</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80024</v>
+        <v>1.83037</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.90225</v>
+        <v>16.93817</v>
       </c>
       <c r="D9" t="n">
-        <v>16.72073</v>
+        <v>16.38182</v>
       </c>
       <c r="E9" t="n">
-        <v>16.71473</v>
+        <v>16.85299</v>
       </c>
       <c r="F9" t="n">
-        <v>41.44706</v>
+        <v>43.48457</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05068</v>
+        <v>0.05016</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81962</v>
+        <v>1.80622</v>
       </c>
     </row>
     <row r="10">
@@ -650,31 +660,51 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.65043</v>
+        <v>16.84814</v>
       </c>
       <c r="D10" t="n">
-        <v>16.5841</v>
+        <v>16.61247</v>
       </c>
       <c r="E10" t="n">
-        <v>16.55323</v>
+        <v>16.68779</v>
       </c>
       <c r="F10" t="n">
-        <v>42.95065</v>
+        <v>41.71767</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05032</v>
+        <v>0.05132</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82155</v>
+        <v>1.8299</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -688,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61129</v>
+        <v>16.66166</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11762</v>
+        <v>16.42144</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.43579</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.23501</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.82009</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60587</v>
+        <v>16.57687</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10228</v>
+        <v>16.54449</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.55901</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.17864</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04994</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.87089</v>
       </c>
     </row>
     <row r="14">
@@ -718,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.58858</v>
+        <v>17.12658</v>
       </c>
       <c r="D14" t="n">
-        <v>1.10308</v>
+        <v>16.69486</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.81556</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.59616</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8108</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.60258</v>
+        <v>16.8016</v>
       </c>
       <c r="D15" t="n">
-        <v>1.11212</v>
+        <v>16.5501</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.74053</v>
+      </c>
+      <c r="F15" t="n">
+        <v>41.75295</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.04953</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.79898</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60812</v>
+        <v>16.82027</v>
       </c>
       <c r="D16" t="n">
-        <v>1.09456</v>
+        <v>16.17012</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.58548</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.73451</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84489</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60716</v>
+        <v>16.86457</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10115</v>
+        <v>16.2628</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.54241</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.90819</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05099</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.81481</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.60598</v>
+        <v>16.77796</v>
       </c>
       <c r="D18" t="n">
-        <v>1.09132</v>
+        <v>16.52861</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.70587</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.04266</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.80116</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60322</v>
+        <v>16.82967</v>
       </c>
       <c r="D19" t="n">
-        <v>1.09739</v>
+        <v>16.30838</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.38884</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.42142</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.79366</v>
       </c>
     </row>
     <row r="20">
@@ -796,51 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60773</v>
+        <v>16.60449</v>
       </c>
       <c r="D20" t="n">
-        <v>1.11869</v>
+        <v>16.17477</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.27212</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.22576</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05086</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.77214</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -852,32 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7601</v>
+        <v>15.6687</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08141</v>
+        <v>15.4467</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60641</v>
+        <v>15.5639</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95304</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10824</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09357</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12741</v>
+        <v>253.41087</v>
       </c>
     </row>
     <row r="23">
@@ -887,28 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.74314</v>
+        <v>15.4938</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08148</v>
+        <v>15.31262</v>
       </c>
       <c r="E23" t="n">
-        <v>0.59611</v>
+        <v>15.36629</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.10843</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09370000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12636</v>
+        <v>251.0695</v>
       </c>
     </row>
     <row r="24">
@@ -918,28 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75117</v>
+        <v>15.83528</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07926999999999999</v>
+        <v>15.37654</v>
       </c>
       <c r="E24" t="n">
-        <v>0.59892</v>
+        <v>15.62191</v>
       </c>
       <c r="F24" t="n">
-        <v>0.94507</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.10963</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09178</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.1257</v>
+        <v>250.36877</v>
       </c>
     </row>
     <row r="25">
@@ -949,28 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.74734</v>
+        <v>15.65774</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08003</v>
+        <v>15.21206</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60261</v>
+        <v>15.58171</v>
       </c>
       <c r="F25" t="n">
-        <v>0.93171</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00729</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09216000000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12737</v>
+        <v>249.88204</v>
       </c>
     </row>
     <row r="26">
@@ -980,28 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75574</v>
+        <v>15.6492</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08042000000000001</v>
+        <v>15.32507</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60249</v>
+        <v>15.40867</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9625899999999999</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.10638</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00744</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09429</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12745</v>
+        <v>254.25667</v>
       </c>
     </row>
     <row r="27">
@@ -1011,28 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.73147</v>
+        <v>15.7706</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08155</v>
+        <v>15.44767</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6010799999999999</v>
+        <v>15.55772</v>
       </c>
       <c r="F27" t="n">
-        <v>0.94757</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.10946</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09203</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12653</v>
+        <v>255.49654</v>
       </c>
     </row>
     <row r="28">
@@ -1042,28 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7521099999999999</v>
+        <v>15.65481</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08173</v>
+        <v>15.42936</v>
       </c>
       <c r="E28" t="n">
-        <v>0.59755</v>
+        <v>15.52032</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96851</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.10951</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00747</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09243</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12485</v>
+        <v>252.67949</v>
       </c>
     </row>
     <row r="29">
@@ -1073,28 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.73104</v>
+        <v>15.52818</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08073</v>
+        <v>15.29116</v>
       </c>
       <c r="E29" t="n">
-        <v>0.61304</v>
+        <v>15.37602</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9503200000000001</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.10748</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09225</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.1247</v>
+        <v>253.17212</v>
       </c>
     </row>
     <row r="30">
@@ -1104,28 +1126,1070 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.74625</v>
+        <v>15.78982</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08056000000000001</v>
+        <v>15.40589</v>
       </c>
       <c r="E30" t="n">
-        <v>0.59924</v>
+        <v>15.77946</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9615</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10995</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I30" t="n">
+        <v>255.62845</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.64488</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.87051</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.03982</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.74476</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.5164</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.83565</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.88564</v>
+      </c>
+      <c r="E33" t="n">
+        <v>15.93101</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.45607</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.52296</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.43959</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.94665</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.40233</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.81607</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.03974</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.48237</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.75971</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.1268</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.39165</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.86739</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.76088</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.04835</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.16075</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.30159</v>
+      </c>
+      <c r="G36" t="n">
+        <v>33.76539</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.66333</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.81768</v>
+      </c>
+      <c r="E37" t="n">
+        <v>15.83448</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.66629</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.14335</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.72203</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.02559</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.39861</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.20586</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33.76723</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.75253</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15.86988</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.28065</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.78582</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.43235</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.55938</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.92085</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.28526</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.15277</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.95371</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.54782</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.88121</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.28767</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.44332</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.26744</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.79503</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.8213</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.45567</v>
+      </c>
+      <c r="F43" t="n">
+        <v>20.97518</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.8756</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.83666</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.06665</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.64001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.78699</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.8003</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.41546</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.95421</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.30923</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.59281</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.82554</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.53519</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.71137</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.32564</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.09511</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.21657</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.64263</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.10123</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.27106</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.80583</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.81111</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.34565</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.06769</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.3176</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.90133</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.2849</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.36947</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.94143</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.23715</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.86012</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.45516</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.36159</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.40489</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.19143</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.32066</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.404</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.60712</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.08739</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.60218</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.10996</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.60615</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.09854</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.61511</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.11424</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60858</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.09105</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.59581</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.11961</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.60129</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.11296</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60604</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.10951</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.60188</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.61167</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.12871</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.59982</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.08215</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.60746</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.12082</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.6103499999999999</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.08739</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.61294</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.11745</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.59829</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.09272</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.61084</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.10585</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.60363</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.07865</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.60171</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.09402</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.7593299999999999</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08011</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.59866</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.97497</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.10881</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12564</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.7460599999999999</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08058</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.93764</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10733</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09307</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1249</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.73503</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.07964</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.60288</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.97385</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10764</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09469</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12478</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.73797</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08115</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.60194</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.92278</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12401</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.74382</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08191</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.61774</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.96413</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.10928</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.08955</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12602</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.7515500000000001</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08096</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.60792</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.95368</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10574</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09134</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12688</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.74707</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.07998</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.6057900000000001</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.9549800000000001</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10683</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I78" t="n">
         <v>0.09257</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.12627</v>
+      <c r="J78" t="n">
+        <v>0.12648</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.73573</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.07988000000000001</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.60829</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.94496</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.10909</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09239</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12836</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.73455</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.07969</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.60275</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.95863</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.10835</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09218</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.1275</v>
       </c>
     </row>
   </sheetData>
